--- a/frontend/docs/Frontend_tests.xlsx
+++ b/frontend/docs/Frontend_tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bpkap\Desktop\er\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Vizsgaremek\frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1CC256-A82A-48CC-9608-2F441D7ECDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2A03EE-0B72-4BEF-A37B-3557E8D51D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8556" yWindow="3360" windowWidth="14484" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7813" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7841" uniqueCount="817">
   <si>
     <t>ID</t>
   </si>
@@ -2744,6 +2744,12 @@
   </si>
   <si>
     <t>After typing the product name nothing gets displayed</t>
+  </si>
+  <si>
+    <t>When the user clicks on the verification button, it seems like it is logged in, but actually it is not</t>
+  </si>
+  <si>
+    <t>Registration succeeds and a confirmation email is sent, user is logged in.</t>
   </si>
 </sst>
 </file>
@@ -2931,7 +2937,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2994,6 +3000,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -15779,7 +15786,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>155</v>
+      </c>
+      <c r="B266" t="s">
+        <v>30</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G266" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H266" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I266" s="26">
+        <v>46128</v>
+      </c>
       <c r="L266" s="5" t="s">
         <v>38</v>
       </c>
@@ -15790,7 +15824,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>156</v>
+      </c>
+      <c r="B267" t="s">
+        <v>30</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G267" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H267" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I267" s="26">
+        <v>46128</v>
+      </c>
       <c r="L267" s="5" t="s">
         <v>38</v>
       </c>
@@ -15801,7 +15862,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>157</v>
+      </c>
+      <c r="B268" t="s">
+        <v>30</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H268" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I268" s="26">
+        <v>46128</v>
+      </c>
       <c r="L268" s="5" t="s">
         <v>38</v>
       </c>
@@ -15812,7 +15900,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>158</v>
+      </c>
+      <c r="B269" t="s">
+        <v>30</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H269" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I269" s="26">
+        <v>46128</v>
+      </c>
       <c r="L269" s="5" t="s">
         <v>38</v>
       </c>

--- a/frontend/docs/Frontend_tests.xlsx
+++ b/frontend/docs/Frontend_tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Vizsgaremek\frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2A03EE-0B72-4BEF-A37B-3557E8D51D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759368E4-3DDF-45DE-8C7F-05A22A69B8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2937,7 +2937,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3000,7 +3000,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -15811,7 +15810,7 @@
       <c r="H266" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I266" s="26">
+      <c r="I266" s="2">
         <v>46128</v>
       </c>
       <c r="L266" s="5" t="s">
@@ -15849,7 +15848,7 @@
       <c r="H267" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I267" s="26">
+      <c r="I267" s="2">
         <v>46128</v>
       </c>
       <c r="L267" s="5" t="s">
@@ -15887,7 +15886,7 @@
       <c r="H268" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I268" s="26">
+      <c r="I268" s="2">
         <v>46128</v>
       </c>
       <c r="L268" s="5" t="s">
@@ -15925,7 +15924,7 @@
       <c r="H269" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I269" s="26">
+      <c r="I269" s="2">
         <v>46128</v>
       </c>
       <c r="L269" s="5" t="s">

--- a/frontend/docs/Frontend_tests.xlsx
+++ b/frontend/docs/Frontend_tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Vizsgaremek\frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020E4846-95A1-4175-9C94-D8CD9FB178CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08914662-A0F9-4A5E-BFC1-979404A6B361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend" sheetId="1" r:id="rId1"/>
@@ -15226,7 +15226,7 @@
     </row>
     <row r="141" spans="1:42" ht="43.2">
       <c r="A141">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="B141" s="22" t="s">
         <v>497</v>
@@ -15277,7 +15277,7 @@
     </row>
     <row r="142" spans="1:42" ht="43.2">
       <c r="A142">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B142" s="22" t="s">
         <v>502</v>
@@ -15328,7 +15328,7 @@
     </row>
     <row r="143" spans="1:42" ht="43.2">
       <c r="A143">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="B143" s="22" t="s">
         <v>507</v>
@@ -15379,7 +15379,7 @@
     </row>
     <row r="144" spans="1:42" ht="43.2">
       <c r="A144">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="B144" s="22" t="s">
         <v>512</v>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="145" spans="1:42" ht="43.2">
       <c r="A145">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="B145" s="22" t="s">
         <v>516</v>
@@ -15481,7 +15481,7 @@
     </row>
     <row r="146" spans="1:42" ht="43.2">
       <c r="A146">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="B146" s="22" t="s">
         <v>521</v>
@@ -15532,7 +15532,7 @@
     </row>
     <row r="147" spans="1:42" ht="43.2">
       <c r="A147">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="B147" s="22" t="s">
         <v>526</v>
@@ -15583,7 +15583,7 @@
     </row>
     <row r="148" spans="1:42" ht="43.2">
       <c r="A148">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="B148" s="22" t="s">
         <v>531</v>
@@ -15634,7 +15634,7 @@
     </row>
     <row r="149" spans="1:42" ht="43.2">
       <c r="A149">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="B149" s="22" t="s">
         <v>536</v>
@@ -15685,7 +15685,7 @@
     </row>
     <row r="150" spans="1:42" ht="43.2">
       <c r="A150">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="B150" s="22" t="s">
         <v>541</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="151" spans="1:42" ht="43.2">
       <c r="A151">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="B151" s="22" t="s">
         <v>546</v>
@@ -15787,7 +15787,7 @@
     </row>
     <row r="152" spans="1:42" ht="28.8">
       <c r="A152">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="B152" s="22" t="s">
         <v>551</v>
@@ -15838,7 +15838,7 @@
     </row>
     <row r="153" spans="1:42" ht="43.2">
       <c r="A153">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="B153" s="22" t="s">
         <v>556</v>
@@ -15889,7 +15889,7 @@
     </row>
     <row r="154" spans="1:42" ht="28.8">
       <c r="A154">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="B154" s="22" t="s">
         <v>561</v>
@@ -15940,7 +15940,7 @@
     </row>
     <row r="155" spans="1:42" ht="28.8">
       <c r="A155">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="B155" s="22" t="s">
         <v>566</v>
@@ -15991,7 +15991,7 @@
     </row>
     <row r="156" spans="1:42" ht="57.6">
       <c r="A156">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="B156" s="22" t="s">
         <v>571</v>
@@ -16042,7 +16042,7 @@
     </row>
     <row r="157" spans="1:42" ht="28.8">
       <c r="A157">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="B157" s="22" t="s">
         <v>576</v>
@@ -16072,7 +16072,7 @@
     </row>
     <row r="158" spans="1:42" ht="28.8">
       <c r="A158">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="B158" s="22" t="s">
         <v>581</v>
@@ -16102,7 +16102,7 @@
     </row>
     <row r="159" spans="1:42" ht="43.2">
       <c r="A159">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="B159" s="22" t="s">
         <v>808</v>
@@ -16132,7 +16132,7 @@
     </row>
     <row r="160" spans="1:42" ht="28.8">
       <c r="A160">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="B160" s="22" t="s">
         <v>803</v>
@@ -16162,7 +16162,7 @@
     </row>
     <row r="161" spans="1:14" ht="28.8">
       <c r="A161">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="B161" s="22" t="s">
         <v>798</v>
@@ -16192,7 +16192,7 @@
     </row>
     <row r="162" spans="1:14" ht="28.8">
       <c r="A162">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="B162" s="22" t="s">
         <v>793</v>
@@ -16222,7 +16222,7 @@
     </row>
     <row r="163" spans="1:14" ht="57.6">
       <c r="A163">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="B163" s="22" t="s">
         <v>788</v>
@@ -16252,7 +16252,7 @@
     </row>
     <row r="164" spans="1:14" ht="57.6">
       <c r="A164">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="B164" s="22" t="s">
         <v>585</v>
@@ -16282,7 +16282,7 @@
     </row>
     <row r="165" spans="1:14" ht="28.8">
       <c r="A165">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="B165" s="22" t="s">
         <v>590</v>
@@ -16312,7 +16312,7 @@
     </row>
     <row r="166" spans="1:14" ht="57.6">
       <c r="A166">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="B166" s="22" t="s">
         <v>595</v>
@@ -16342,7 +16342,7 @@
     </row>
     <row r="167" spans="1:14" ht="28.8">
       <c r="A167">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="B167" s="22" t="s">
         <v>600</v>
@@ -16372,7 +16372,7 @@
     </row>
     <row r="168" spans="1:14" ht="28.8">
       <c r="A168">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="B168" s="22" t="s">
         <v>605</v>
@@ -16402,7 +16402,7 @@
     </row>
     <row r="169" spans="1:14" ht="28.8">
       <c r="A169">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="B169" s="22" t="s">
         <v>610</v>
@@ -16432,7 +16432,7 @@
     </row>
     <row r="170" spans="1:14" ht="43.2">
       <c r="A170">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="B170" s="22" t="s">
         <v>615</v>
@@ -16462,7 +16462,7 @@
     </row>
     <row r="171" spans="1:14" ht="43.2">
       <c r="A171">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B171" s="22" t="s">
         <v>620</v>
@@ -16492,7 +16492,7 @@
     </row>
     <row r="172" spans="1:14" ht="43.2">
       <c r="A172">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="B172" s="22" t="s">
         <v>625</v>
@@ -16522,7 +16522,7 @@
     </row>
     <row r="173" spans="1:14" ht="28.8">
       <c r="A173">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="B173" s="22" t="s">
         <v>630</v>
@@ -16552,7 +16552,7 @@
     </row>
     <row r="174" spans="1:14" ht="28.8">
       <c r="A174">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="B174" s="22" t="s">
         <v>635</v>
@@ -16582,7 +16582,7 @@
     </row>
     <row r="175" spans="1:14" ht="28.8">
       <c r="A175">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="B175" s="22" t="s">
         <v>640</v>
@@ -16612,7 +16612,7 @@
     </row>
     <row r="176" spans="1:14" ht="43.2">
       <c r="A176">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="B176" s="22" t="s">
         <v>645</v>
@@ -16642,7 +16642,7 @@
     </row>
     <row r="177" spans="1:14" ht="28.8">
       <c r="A177">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="B177" s="22" t="s">
         <v>778</v>
@@ -16672,7 +16672,7 @@
     </row>
     <row r="178" spans="1:14" ht="28.8">
       <c r="A178">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="B178" s="22" t="s">
         <v>774</v>
@@ -16702,7 +16702,7 @@
     </row>
     <row r="179" spans="1:14" ht="43.2">
       <c r="A179">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="B179" s="22" t="s">
         <v>769</v>
@@ -16732,7 +16732,7 @@
     </row>
     <row r="180" spans="1:14" ht="28.8">
       <c r="A180">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="B180" s="22" t="s">
         <v>764</v>
@@ -16762,7 +16762,7 @@
     </row>
     <row r="181" spans="1:14" ht="28.8">
       <c r="A181">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="B181" s="22" t="s">
         <v>759</v>
@@ -16792,7 +16792,7 @@
     </row>
     <row r="182" spans="1:14" ht="57.6">
       <c r="A182">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="B182" s="22" t="s">
         <v>754</v>
@@ -16822,7 +16822,7 @@
     </row>
     <row r="183" spans="1:14" ht="28.8">
       <c r="A183">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="B183" s="22" t="s">
         <v>749</v>
@@ -16852,7 +16852,7 @@
     </row>
     <row r="184" spans="1:14" ht="28.8">
       <c r="A184">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="B184" s="22" t="s">
         <v>744</v>
@@ -16882,7 +16882,7 @@
     </row>
     <row r="185" spans="1:14" ht="43.2">
       <c r="A185">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="B185" s="22" t="s">
         <v>739</v>
@@ -16912,7 +16912,7 @@
     </row>
     <row r="186" spans="1:14" ht="28.8">
       <c r="A186">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="B186" s="22" t="s">
         <v>734</v>
@@ -16942,7 +16942,7 @@
     </row>
     <row r="187" spans="1:14" ht="43.2">
       <c r="A187">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="B187" s="22" t="s">
         <v>729</v>
@@ -16972,7 +16972,7 @@
     </row>
     <row r="188" spans="1:14" ht="28.8">
       <c r="A188">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="B188" s="22" t="s">
         <v>724</v>
@@ -17002,7 +17002,7 @@
     </row>
     <row r="189" spans="1:14" ht="43.2">
       <c r="A189">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B189" s="22" t="s">
         <v>719</v>
@@ -17032,7 +17032,7 @@
     </row>
     <row r="190" spans="1:14" ht="28.8">
       <c r="A190">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="B190" s="22" t="s">
         <v>714</v>
@@ -17062,7 +17062,7 @@
     </row>
     <row r="191" spans="1:14" ht="43.2">
       <c r="A191">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="B191" s="22" t="s">
         <v>709</v>
@@ -17092,7 +17092,7 @@
     </row>
     <row r="192" spans="1:14" ht="43.2">
       <c r="A192">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="B192" s="22" t="s">
         <v>704</v>
@@ -17122,7 +17122,7 @@
     </row>
     <row r="193" spans="1:14" ht="43.2">
       <c r="A193">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B193" s="22" t="s">
         <v>699</v>
@@ -17152,7 +17152,7 @@
     </row>
     <row r="194" spans="1:14" ht="28.8">
       <c r="A194">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="B194" s="22" t="s">
         <v>695</v>
@@ -17182,7 +17182,7 @@
     </row>
     <row r="195" spans="1:14" ht="28.8">
       <c r="A195">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="B195" s="22" t="s">
         <v>690</v>
@@ -17212,7 +17212,7 @@
     </row>
     <row r="196" spans="1:14" ht="28.8">
       <c r="A196">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="B196" s="22" t="s">
         <v>685</v>
@@ -17242,7 +17242,7 @@
     </row>
     <row r="197" spans="1:14" ht="28.8">
       <c r="A197">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="B197" s="22" t="s">
         <v>680</v>
@@ -17272,7 +17272,7 @@
     </row>
     <row r="198" spans="1:14" ht="28.8">
       <c r="A198">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="B198" s="22" t="s">
         <v>675</v>
@@ -17302,7 +17302,7 @@
     </row>
     <row r="199" spans="1:14" ht="43.2">
       <c r="A199">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="B199" s="22" t="s">
         <v>670</v>
@@ -17332,7 +17332,7 @@
     </row>
     <row r="200" spans="1:14" ht="28.8">
       <c r="A200">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="B200" s="22" t="s">
         <v>665</v>
@@ -17362,7 +17362,7 @@
     </row>
     <row r="201" spans="1:14" ht="28.8">
       <c r="A201">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="B201" s="22" t="s">
         <v>660</v>
@@ -17392,7 +17392,7 @@
     </row>
     <row r="202" spans="1:14" ht="57.6">
       <c r="A202">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="B202" s="22" t="s">
         <v>655</v>
@@ -17422,7 +17422,7 @@
     </row>
     <row r="203" spans="1:14" ht="28.8">
       <c r="A203">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="B203" s="22" t="s">
         <v>497</v>
@@ -17454,7 +17454,7 @@
     </row>
     <row r="204" spans="1:14" ht="43.2">
       <c r="A204">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="B204" s="22" t="s">
         <v>502</v>
@@ -17486,7 +17486,7 @@
     </row>
     <row r="205" spans="1:14" ht="28.8">
       <c r="A205">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="B205" s="22" t="s">
         <v>507</v>
@@ -17518,7 +17518,7 @@
     </row>
     <row r="206" spans="1:14" ht="43.2">
       <c r="A206">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="B206" s="22" t="s">
         <v>512</v>
@@ -17550,7 +17550,7 @@
     </row>
     <row r="207" spans="1:14" ht="43.2">
       <c r="A207">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="B207" s="22" t="s">
         <v>516</v>
@@ -17582,7 +17582,7 @@
     </row>
     <row r="208" spans="1:14" ht="43.2">
       <c r="A208">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="B208" s="22" t="s">
         <v>516</v>
@@ -17614,7 +17614,7 @@
     </row>
     <row r="209" spans="1:14" ht="43.2">
       <c r="A209">
-        <v>98</v>
+        <v>208</v>
       </c>
       <c r="B209" s="22" t="s">
         <v>521</v>
@@ -17646,7 +17646,7 @@
     </row>
     <row r="210" spans="1:14" ht="28.8">
       <c r="A210">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="B210" s="22" t="s">
         <v>526</v>
@@ -17678,7 +17678,7 @@
     </row>
     <row r="211" spans="1:14" ht="43.2">
       <c r="A211">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="B211" s="22" t="s">
         <v>531</v>
@@ -17708,7 +17708,7 @@
     </row>
     <row r="212" spans="1:14" ht="43.2">
       <c r="A212">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="B212" s="22" t="s">
         <v>536</v>
@@ -17738,7 +17738,7 @@
     </row>
     <row r="213" spans="1:14" ht="43.2">
       <c r="A213">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="B213" s="22" t="s">
         <v>541</v>
@@ -17768,7 +17768,7 @@
     </row>
     <row r="214" spans="1:14" ht="43.2">
       <c r="A214">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="B214" s="22" t="s">
         <v>546</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="215" spans="1:14" ht="28.8">
       <c r="A215">
-        <v>104</v>
+        <v>214</v>
       </c>
       <c r="B215" s="22" t="s">
         <v>551</v>
@@ -17828,7 +17828,7 @@
     </row>
     <row r="216" spans="1:14" ht="28.8">
       <c r="A216">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="B216" s="22" t="s">
         <v>556</v>
@@ -17858,7 +17858,7 @@
     </row>
     <row r="217" spans="1:14" ht="28.8">
       <c r="A217">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="B217" s="22" t="s">
         <v>561</v>
@@ -17888,7 +17888,7 @@
     </row>
     <row r="218" spans="1:14" ht="28.8">
       <c r="A218">
-        <v>107</v>
+        <v>217</v>
       </c>
       <c r="B218" s="22" t="s">
         <v>566</v>
@@ -17918,7 +17918,7 @@
     </row>
     <row r="219" spans="1:14" ht="57.6">
       <c r="A219">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="B219" s="22" t="s">
         <v>571</v>
@@ -17948,7 +17948,7 @@
     </row>
     <row r="220" spans="1:14" ht="28.8">
       <c r="A220">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="B220" s="22" t="s">
         <v>576</v>
@@ -17978,7 +17978,7 @@
     </row>
     <row r="221" spans="1:14" ht="28.8">
       <c r="A221">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="B221" s="22" t="s">
         <v>581</v>
@@ -18008,7 +18008,7 @@
     </row>
     <row r="222" spans="1:14" ht="43.2">
       <c r="A222">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="B222" s="22" t="s">
         <v>808</v>
@@ -18038,7 +18038,7 @@
     </row>
     <row r="223" spans="1:14" ht="28.8">
       <c r="A223">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="B223" s="22" t="s">
         <v>803</v>
@@ -18068,7 +18068,7 @@
     </row>
     <row r="224" spans="1:14" ht="28.8">
       <c r="A224">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="B224" s="22" t="s">
         <v>798</v>
@@ -18098,7 +18098,7 @@
     </row>
     <row r="225" spans="1:14" ht="28.8">
       <c r="A225">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c r="B225" s="22" t="s">
         <v>793</v>
@@ -18128,7 +18128,7 @@
     </row>
     <row r="226" spans="1:14" ht="57.6">
       <c r="A226">
-        <v>115</v>
+        <v>225</v>
       </c>
       <c r="B226" s="22" t="s">
         <v>788</v>
@@ -18158,7 +18158,7 @@
     </row>
     <row r="227" spans="1:14" ht="57.6">
       <c r="A227">
-        <v>116</v>
+        <v>226</v>
       </c>
       <c r="B227" s="22" t="s">
         <v>585</v>
@@ -18188,7 +18188,7 @@
     </row>
     <row r="228" spans="1:14" ht="28.8">
       <c r="A228">
-        <v>117</v>
+        <v>227</v>
       </c>
       <c r="B228" s="22" t="s">
         <v>590</v>
@@ -18218,7 +18218,7 @@
     </row>
     <row r="229" spans="1:14" ht="57.6">
       <c r="A229">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="B229" s="22" t="s">
         <v>595</v>
@@ -18248,7 +18248,7 @@
     </row>
     <row r="230" spans="1:14" ht="28.8">
       <c r="A230">
-        <v>119</v>
+        <v>229</v>
       </c>
       <c r="B230" s="22" t="s">
         <v>600</v>
@@ -18278,7 +18278,7 @@
     </row>
     <row r="231" spans="1:14" ht="28.8">
       <c r="A231">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="B231" s="22" t="s">
         <v>605</v>
@@ -18308,7 +18308,7 @@
     </row>
     <row r="232" spans="1:14" ht="28.8">
       <c r="A232">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="B232" s="22" t="s">
         <v>610</v>
@@ -18338,7 +18338,7 @@
     </row>
     <row r="233" spans="1:14" ht="43.2">
       <c r="A233">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="B233" s="22" t="s">
         <v>615</v>
@@ -18368,7 +18368,7 @@
     </row>
     <row r="234" spans="1:14" ht="43.2">
       <c r="A234">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="B234" s="22" t="s">
         <v>620</v>
@@ -18398,7 +18398,7 @@
     </row>
     <row r="235" spans="1:14" ht="43.2">
       <c r="A235">
-        <v>124</v>
+        <v>234</v>
       </c>
       <c r="B235" s="22" t="s">
         <v>625</v>
@@ -18428,7 +18428,7 @@
     </row>
     <row r="236" spans="1:14" ht="28.8">
       <c r="A236">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="B236" s="22" t="s">
         <v>630</v>
@@ -18458,7 +18458,7 @@
     </row>
     <row r="237" spans="1:14" ht="28.8">
       <c r="A237">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="B237" s="22" t="s">
         <v>635</v>
@@ -18488,7 +18488,7 @@
     </row>
     <row r="238" spans="1:14" ht="28.8">
       <c r="A238">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="B238" s="22" t="s">
         <v>640</v>
@@ -18518,7 +18518,7 @@
     </row>
     <row r="239" spans="1:14" ht="43.2">
       <c r="A239">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="B239" s="22" t="s">
         <v>645</v>
@@ -18548,7 +18548,7 @@
     </row>
     <row r="240" spans="1:14" ht="28.8">
       <c r="A240">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="B240" s="22" t="s">
         <v>778</v>
@@ -18578,7 +18578,7 @@
     </row>
     <row r="241" spans="1:14" ht="28.8">
       <c r="A241">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="B241" s="22" t="s">
         <v>774</v>
@@ -18608,7 +18608,7 @@
     </row>
     <row r="242" spans="1:14" ht="43.2">
       <c r="A242">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="B242" s="22" t="s">
         <v>769</v>
@@ -18638,7 +18638,7 @@
     </row>
     <row r="243" spans="1:14" ht="28.8">
       <c r="A243">
-        <v>132</v>
+        <v>242</v>
       </c>
       <c r="B243" s="22" t="s">
         <v>764</v>
@@ -18668,7 +18668,7 @@
     </row>
     <row r="244" spans="1:14" ht="28.8">
       <c r="A244">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="B244" s="22" t="s">
         <v>759</v>
@@ -18698,7 +18698,7 @@
     </row>
     <row r="245" spans="1:14" ht="57.6">
       <c r="A245">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="B245" s="22" t="s">
         <v>754</v>
@@ -18728,7 +18728,7 @@
     </row>
     <row r="246" spans="1:14" ht="28.8">
       <c r="A246">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="B246" s="22" t="s">
         <v>749</v>
@@ -18758,7 +18758,7 @@
     </row>
     <row r="247" spans="1:14" ht="28.8">
       <c r="A247">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="B247" s="22" t="s">
         <v>744</v>
@@ -18788,7 +18788,7 @@
     </row>
     <row r="248" spans="1:14" ht="43.2">
       <c r="A248">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="B248" s="22" t="s">
         <v>739</v>
@@ -18818,7 +18818,7 @@
     </row>
     <row r="249" spans="1:14" ht="28.8">
       <c r="A249">
-        <v>138</v>
+        <v>248</v>
       </c>
       <c r="B249" s="22" t="s">
         <v>734</v>
@@ -18848,7 +18848,7 @@
     </row>
     <row r="250" spans="1:14" ht="43.2">
       <c r="A250">
-        <v>139</v>
+        <v>249</v>
       </c>
       <c r="B250" s="22" t="s">
         <v>729</v>
@@ -18878,7 +18878,7 @@
     </row>
     <row r="251" spans="1:14" ht="28.8">
       <c r="A251">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="B251" s="22" t="s">
         <v>724</v>
@@ -18908,7 +18908,7 @@
     </row>
     <row r="252" spans="1:14" ht="43.2">
       <c r="A252">
-        <v>141</v>
+        <v>251</v>
       </c>
       <c r="B252" s="22" t="s">
         <v>719</v>
@@ -18938,7 +18938,7 @@
     </row>
     <row r="253" spans="1:14" ht="28.8">
       <c r="A253">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="B253" s="22" t="s">
         <v>714</v>
@@ -18968,7 +18968,7 @@
     </row>
     <row r="254" spans="1:14" ht="43.2">
       <c r="A254">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="B254" s="22" t="s">
         <v>709</v>
@@ -18998,7 +18998,7 @@
     </row>
     <row r="255" spans="1:14" ht="43.2">
       <c r="A255">
-        <v>144</v>
+        <v>254</v>
       </c>
       <c r="B255" s="22" t="s">
         <v>704</v>
@@ -19028,7 +19028,7 @@
     </row>
     <row r="256" spans="1:14" ht="43.2">
       <c r="A256">
-        <v>145</v>
+        <v>255</v>
       </c>
       <c r="B256" s="22" t="s">
         <v>699</v>
@@ -19058,7 +19058,7 @@
     </row>
     <row r="257" spans="1:14" ht="28.8">
       <c r="A257">
-        <v>146</v>
+        <v>256</v>
       </c>
       <c r="B257" s="22" t="s">
         <v>695</v>
@@ -19088,7 +19088,7 @@
     </row>
     <row r="258" spans="1:14" ht="28.8">
       <c r="A258">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="B258" s="22" t="s">
         <v>690</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="259" spans="1:14" ht="28.8">
       <c r="A259">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="B259" s="22" t="s">
         <v>685</v>
@@ -19148,7 +19148,7 @@
     </row>
     <row r="260" spans="1:14" ht="28.8">
       <c r="A260">
-        <v>149</v>
+        <v>259</v>
       </c>
       <c r="B260" s="22" t="s">
         <v>680</v>
@@ -19178,7 +19178,7 @@
     </row>
     <row r="261" spans="1:14" ht="28.8">
       <c r="A261">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="B261" s="22" t="s">
         <v>675</v>
@@ -19208,7 +19208,7 @@
     </row>
     <row r="262" spans="1:14" ht="43.2">
       <c r="A262">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="B262" s="22" t="s">
         <v>670</v>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="263" spans="1:14" ht="28.8">
       <c r="A263">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="B263" s="22" t="s">
         <v>665</v>
@@ -19268,7 +19268,7 @@
     </row>
     <row r="264" spans="1:14" ht="28.8">
       <c r="A264">
-        <v>153</v>
+        <v>263</v>
       </c>
       <c r="B264" s="22" t="s">
         <v>660</v>
@@ -19298,7 +19298,7 @@
     </row>
     <row r="265" spans="1:14" ht="57.6">
       <c r="A265">
-        <v>154</v>
+        <v>264</v>
       </c>
       <c r="B265" s="22" t="s">
         <v>655</v>
@@ -19328,7 +19328,7 @@
     </row>
     <row r="266" spans="1:14" ht="57.6">
       <c r="A266">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="B266" t="s">
         <v>30</v>
@@ -19360,7 +19360,7 @@
     </row>
     <row r="267" spans="1:14" ht="57.6">
       <c r="A267">
-        <v>156</v>
+        <v>266</v>
       </c>
       <c r="B267" t="s">
         <v>30</v>
@@ -19392,7 +19392,7 @@
     </row>
     <row r="268" spans="1:14" ht="57.6">
       <c r="A268">
-        <v>157</v>
+        <v>267</v>
       </c>
       <c r="B268" t="s">
         <v>30</v>
@@ -19424,7 +19424,7 @@
     </row>
     <row r="269" spans="1:14" ht="57.6">
       <c r="A269">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="B269" t="s">
         <v>30</v>
